--- a/artfynd/A 2524-2026 artfynd.xlsx
+++ b/artfynd/A 2524-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131054136</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131054138</v>
       </c>
       <c r="B3" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131054137</v>
       </c>
       <c r="B4" t="n">
-        <v>92038</v>
+        <v>92040</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>131054135</v>
       </c>
       <c r="B5" t="n">
-        <v>92237</v>
+        <v>92239</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2524-2026 artfynd.xlsx
+++ b/artfynd/A 2524-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131054136</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131054138</v>
       </c>
       <c r="B3" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131054137</v>
       </c>
       <c r="B4" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>131054135</v>
       </c>
       <c r="B5" t="n">
-        <v>92239</v>
+        <v>92240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2524-2026 artfynd.xlsx
+++ b/artfynd/A 2524-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131054138</v>
+        <v>131054137</v>
       </c>
       <c r="B2" t="n">
-        <v>57076</v>
+        <v>92134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1106</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660731</v>
+        <v>660716</v>
       </c>
       <c r="R2" t="n">
-        <v>6661229</v>
+        <v>6661084</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 tuppar</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131054136</v>
+        <v>131054135</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>92333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660622</v>
+        <v>660554</v>
       </c>
       <c r="R3" t="n">
-        <v>6661065</v>
+        <v>6661098</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131054137</v>
+        <v>131054136</v>
       </c>
       <c r="B4" t="n">
-        <v>92042</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1106</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>660716</v>
+        <v>660622</v>
       </c>
       <c r="R4" t="n">
-        <v>6661084</v>
+        <v>6661065</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131054135</v>
+        <v>131054138</v>
       </c>
       <c r="B5" t="n">
-        <v>92241</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660554</v>
+        <v>660731</v>
       </c>
       <c r="R5" t="n">
-        <v>6661098</v>
+        <v>6661229</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>2 tuppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
